--- a/public/example.xlsx
+++ b/public/example.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\projects\laravel\financial-assistant-service\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\workspace\Laravel\cyfgs-brocon-financial-assistance\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE724AA-A138-4B82-829A-F082CA0C6DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -85,12 +86,30 @@
   </si>
   <si>
     <t>Developer</t>
+  </si>
+  <si>
+    <t>lewis@gmail.com</t>
+  </si>
+  <si>
+    <t>Buea</t>
+  </si>
+  <si>
+    <t>Bill Clinton</t>
+  </si>
+  <si>
+    <t>billclinyon@gmail.com</t>
+  </si>
+  <si>
+    <t>Bright Pat</t>
+  </si>
+  <si>
+    <t>bright@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -145,16 +164,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -370,19 +387,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -402,14 +419,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>674049243</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -422,14 +439,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>67609920</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -442,15 +459,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C4">
-        <v>237673660071</v>
+        <v>670660071</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -462,14 +479,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>678934023</v>
       </c>
       <c r="D5" t="s">
@@ -482,10 +499,94 @@
         <v>21</v>
       </c>
     </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3">
+        <v>678234561</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2">
+        <v>677809232</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>670060071</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2">
+        <v>678934023</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1"/>
-    <hyperlink ref="B5" r:id="rId2"/>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{814D70BC-6DF2-46BD-A052-3CEEE84DECA7}"/>
+    <hyperlink ref="B9" r:id="rId4" xr:uid="{ACCDCF04-EA7E-40CD-99AB-5F92498DF017}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{27C2FA85-9E29-401C-A6BF-DBAE167BA2B9}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{F540E30D-431F-4CC9-A3C0-73D7AEE4D4E9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/example.xlsx
+++ b/public/example.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\workspace\Laravel\cyfgs-brocon-financial-assistance\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE724AA-A138-4B82-829A-F082CA0C6DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA85666-7767-44C2-A3FE-263400CF0693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -104,6 +104,42 @@
   </si>
   <si>
     <t>bright@gmail.com</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>peterjerry</t>
+  </si>
+  <si>
+    <t>lewisshalla</t>
+  </si>
+  <si>
+    <t>patterson</t>
+  </si>
+  <si>
+    <t>abramjoe</t>
+  </si>
+  <si>
+    <t>billclinton</t>
+  </si>
+  <si>
+    <t>Nforbi Nji</t>
+  </si>
+  <si>
+    <t>nforbinji</t>
+  </si>
+  <si>
+    <t>brightpat</t>
+  </si>
+  <si>
+    <t>Williams Kennedy</t>
+  </si>
+  <si>
+    <t>williamkennedy@gmail.com</t>
+  </si>
+  <si>
+    <t>williamskennedy</t>
   </si>
 </sst>
 </file>
@@ -391,7 +427,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5703125" customWidth="1"/>
@@ -399,7 +435,7 @@
     <col min="3" max="3" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,8 +454,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -438,8 +477,11 @@
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="G2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -458,8 +500,11 @@
       <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G3" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -478,8 +523,11 @@
       <c r="F4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -498,8 +546,11 @@
       <c r="F5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
@@ -518,10 +569,13 @@
       <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>22</v>
@@ -538,8 +592,11 @@
       <c r="F7" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G7" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -558,16 +615,19 @@
       <c r="F8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2">
-        <v>678934023</v>
+        <v>670034023</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -577,6 +637,9 @@
       </c>
       <c r="F9" t="s">
         <v>23</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
